--- a/data/2026_06_05_sql_data_frame_creation_with_curated_subsets/subset_4/labeling.xlsx
+++ b/data/2026_06_05_sql_data_frame_creation_with_curated_subsets/subset_4/labeling.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cgiar-my.sharepoint.com/personal/m_penuela_cgiar_org/Documents/Documents/projects/lmf/data/data_organization_june/subset_4/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="11_F25DC773A252ABDACC10486279DD55085BDE58F2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8893EC9E-008F-4ADE-B586-5FE93A5ABD05}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="11_F25DC773A252ABDACC10486279DD55085BDE58F2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ABAA36F3-AFCF-44F0-89B7-40058280FC0B}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19090" yWindow="-8270" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,9 +36,6 @@
     <t>10_requisitioner</t>
   </si>
   <si>
-    <t>10_set_cait</t>
-  </si>
-  <si>
     <t>10_ciat_lab_id</t>
   </si>
   <si>
@@ -598,6 +595,9 @@
   </si>
   <si>
     <t>40_result_q_raw_data</t>
+  </si>
+  <si>
+    <t>10_set_ciat</t>
   </si>
 </sst>
 </file>
@@ -650,6 +650,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -916,14 +920,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:AV21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="2" spans="1:48" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:48" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:48" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:48" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -934,714 +938,714 @@
         <v>2</v>
       </c>
       <c r="D3" t="s">
+        <v>190</v>
+      </c>
+      <c r="E3" t="s">
         <v>3</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>4</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>5</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>6</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
         <v>7</v>
       </c>
-      <c r="I3" t="s">
+      <c r="J3" t="s">
         <v>8</v>
       </c>
-      <c r="J3" t="s">
+      <c r="K3" t="s">
         <v>9</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
         <v>10</v>
       </c>
-      <c r="L3" t="s">
+      <c r="M3" t="s">
         <v>11</v>
       </c>
-      <c r="M3" t="s">
+      <c r="N3" t="s">
         <v>12</v>
       </c>
-      <c r="N3" t="s">
+      <c r="O3" t="s">
         <v>13</v>
       </c>
-      <c r="O3" t="s">
+      <c r="P3" t="s">
         <v>14</v>
       </c>
-      <c r="P3" t="s">
+    </row>
+    <row r="4" spans="1:48" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
         <v>15</v>
       </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J4" t="s">
+        <v>24</v>
+      </c>
+      <c r="K4" t="s">
+        <v>25</v>
+      </c>
+      <c r="L4" t="s">
+        <v>26</v>
+      </c>
+      <c r="M4" t="s">
+        <v>27</v>
+      </c>
+      <c r="N4" t="s">
+        <v>28</v>
+      </c>
+      <c r="O4" t="s">
+        <v>29</v>
+      </c>
     </row>
-    <row r="4" spans="1:48" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+    <row r="8" spans="1:48" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="9" spans="1:48" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" t="s">
+        <v>34</v>
+      </c>
+      <c r="E9" t="s">
+        <v>35</v>
+      </c>
+      <c r="F9" t="s">
+        <v>36</v>
+      </c>
+      <c r="G9" t="s">
+        <v>37</v>
+      </c>
+      <c r="H9" t="s">
+        <v>38</v>
+      </c>
+      <c r="I9" t="s">
+        <v>39</v>
+      </c>
+      <c r="J9" t="s">
+        <v>40</v>
+      </c>
+      <c r="K9" t="s">
+        <v>41</v>
+      </c>
+      <c r="L9" t="s">
+        <v>42</v>
+      </c>
+      <c r="M9" t="s">
+        <v>43</v>
+      </c>
+      <c r="N9" t="s">
+        <v>44</v>
+      </c>
+      <c r="O9" t="s">
+        <v>45</v>
+      </c>
+      <c r="P9" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>47</v>
+      </c>
+      <c r="R9" t="s">
+        <v>48</v>
+      </c>
+      <c r="S9" t="s">
+        <v>49</v>
+      </c>
+      <c r="T9" t="s">
+        <v>50</v>
+      </c>
+      <c r="U9" t="s">
+        <v>51</v>
+      </c>
+      <c r="V9" t="s">
+        <v>52</v>
+      </c>
+      <c r="W9" t="s">
+        <v>53</v>
+      </c>
+      <c r="X9" t="s">
+        <v>54</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>55</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA9" t="s">
+        <v>57</v>
+      </c>
+      <c r="AB9" t="s">
+        <v>58</v>
+      </c>
+      <c r="AC9" t="s">
+        <v>59</v>
+      </c>
+      <c r="AD9" t="s">
+        <v>60</v>
+      </c>
+      <c r="AE9" t="s">
+        <v>61</v>
+      </c>
+      <c r="AF9" t="s">
+        <v>62</v>
+      </c>
+      <c r="AG9" t="s">
+        <v>63</v>
+      </c>
+      <c r="AH9" t="s">
+        <v>64</v>
+      </c>
+      <c r="AI9" t="s">
+        <v>65</v>
+      </c>
+      <c r="AJ9" t="s">
+        <v>66</v>
+      </c>
+      <c r="AK9" t="s">
+        <v>67</v>
+      </c>
+      <c r="AL9" t="s">
+        <v>68</v>
+      </c>
+      <c r="AM9" t="s">
+        <v>69</v>
+      </c>
+      <c r="AN9" t="s">
+        <v>70</v>
+      </c>
+      <c r="AO9" t="s">
+        <v>71</v>
+      </c>
+      <c r="AP9" t="s">
+        <v>72</v>
+      </c>
+      <c r="AQ9" t="s">
+        <v>73</v>
+      </c>
+      <c r="AR9" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS9" t="s">
+        <v>75</v>
+      </c>
+      <c r="AT9" t="s">
+        <v>76</v>
+      </c>
+      <c r="AU9" t="s">
+        <v>77</v>
+      </c>
+      <c r="AV9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="10" spans="1:48" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>79</v>
+      </c>
+      <c r="B10" t="s">
+        <v>80</v>
+      </c>
+      <c r="C10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" t="s">
+        <v>81</v>
+      </c>
+      <c r="E10" t="s">
+        <v>21</v>
+      </c>
+      <c r="F10" t="s">
+        <v>22</v>
+      </c>
+      <c r="G10" t="s">
+        <v>23</v>
+      </c>
+      <c r="H10" t="s">
+        <v>24</v>
+      </c>
+      <c r="I10" t="s">
+        <v>25</v>
+      </c>
+      <c r="J10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K10" t="s">
+        <v>82</v>
+      </c>
+      <c r="L10" t="s">
+        <v>18</v>
+      </c>
+      <c r="M10" t="s">
+        <v>83</v>
+      </c>
+      <c r="N10" t="s">
+        <v>84</v>
+      </c>
+      <c r="O10" t="s">
+        <v>85</v>
+      </c>
+      <c r="P10" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>87</v>
+      </c>
+      <c r="R10" t="s">
+        <v>88</v>
+      </c>
+      <c r="S10" t="s">
+        <v>89</v>
+      </c>
+      <c r="T10" t="s">
+        <v>90</v>
+      </c>
+      <c r="U10" t="s">
+        <v>91</v>
+      </c>
+      <c r="V10" t="s">
+        <v>92</v>
+      </c>
+      <c r="W10" t="s">
+        <v>93</v>
+      </c>
+      <c r="X10" t="s">
+        <v>94</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>95</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>96</v>
+      </c>
+      <c r="AA10" t="s">
+        <v>97</v>
+      </c>
+      <c r="AB10" t="s">
+        <v>98</v>
+      </c>
+      <c r="AC10" t="s">
+        <v>99</v>
+      </c>
+      <c r="AD10" t="s">
+        <v>100</v>
+      </c>
+      <c r="AE10" t="s">
+        <v>101</v>
+      </c>
+      <c r="AF10" t="s">
+        <v>102</v>
+      </c>
+      <c r="AG10" t="s">
+        <v>103</v>
+      </c>
+      <c r="AH10" t="s">
+        <v>104</v>
+      </c>
+      <c r="AI10" t="s">
+        <v>105</v>
+      </c>
+      <c r="AJ10" t="s">
+        <v>106</v>
+      </c>
+      <c r="AK10" t="s">
+        <v>107</v>
+      </c>
+      <c r="AL10" t="s">
+        <v>108</v>
+      </c>
+      <c r="AM10" t="s">
+        <v>109</v>
+      </c>
+      <c r="AN10" t="s">
+        <v>110</v>
+      </c>
+      <c r="AO10" t="s">
+        <v>111</v>
+      </c>
+      <c r="AP10" t="s">
+        <v>112</v>
+      </c>
+      <c r="AQ10" t="s">
+        <v>113</v>
+      </c>
+      <c r="AR10" t="s">
+        <v>114</v>
+      </c>
+      <c r="AS10" t="s">
+        <v>115</v>
+      </c>
+      <c r="AT10" t="s">
+        <v>116</v>
+      </c>
+      <c r="AU10" t="s">
+        <v>117</v>
+      </c>
+      <c r="AV10" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="14" spans="1:48" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="15" spans="1:48" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>119</v>
+      </c>
+      <c r="B15" t="s">
+        <v>120</v>
+      </c>
+      <c r="C15" t="s">
+        <v>121</v>
+      </c>
+      <c r="D15" t="s">
+        <v>122</v>
+      </c>
+      <c r="E15" t="s">
+        <v>123</v>
+      </c>
+      <c r="F15" t="s">
+        <v>124</v>
+      </c>
+      <c r="G15" t="s">
+        <v>125</v>
+      </c>
+      <c r="H15" t="s">
+        <v>126</v>
+      </c>
+      <c r="I15" t="s">
+        <v>127</v>
+      </c>
+      <c r="J15" t="s">
+        <v>128</v>
+      </c>
+      <c r="K15" t="s">
+        <v>129</v>
+      </c>
+      <c r="L15" t="s">
+        <v>130</v>
+      </c>
+      <c r="M15" t="s">
+        <v>131</v>
+      </c>
+      <c r="N15" t="s">
+        <v>132</v>
+      </c>
+      <c r="O15" t="s">
+        <v>133</v>
+      </c>
+      <c r="P15" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>135</v>
+      </c>
+      <c r="R15" t="s">
+        <v>136</v>
+      </c>
+      <c r="S15" t="s">
+        <v>137</v>
+      </c>
+      <c r="T15" t="s">
+        <v>138</v>
+      </c>
+      <c r="U15" t="s">
+        <v>139</v>
+      </c>
+      <c r="V15" t="s">
+        <v>140</v>
+      </c>
+      <c r="W15" t="s">
+        <v>141</v>
+      </c>
+      <c r="X15" t="s">
+        <v>142</v>
+      </c>
+      <c r="Y15" t="s">
+        <v>143</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>144</v>
+      </c>
+      <c r="AA15" t="s">
+        <v>145</v>
+      </c>
+      <c r="AB15" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="16" spans="1:48" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>79</v>
+      </c>
+      <c r="B16" t="s">
+        <v>80</v>
+      </c>
+      <c r="C16" t="s">
+        <v>80</v>
+      </c>
+      <c r="D16" t="s">
+        <v>17</v>
+      </c>
+      <c r="E16" t="s">
+        <v>81</v>
+      </c>
+      <c r="F16" t="s">
+        <v>21</v>
+      </c>
+      <c r="G16" t="s">
+        <v>22</v>
+      </c>
+      <c r="H16" t="s">
+        <v>23</v>
+      </c>
+      <c r="I16" t="s">
+        <v>24</v>
+      </c>
+      <c r="J16" t="s">
+        <v>25</v>
+      </c>
+      <c r="K16" t="s">
+        <v>26</v>
+      </c>
+      <c r="L16" t="s">
+        <v>82</v>
+      </c>
+      <c r="M16" t="s">
+        <v>18</v>
+      </c>
+      <c r="N16" t="s">
+        <v>83</v>
+      </c>
+      <c r="O16" t="s">
+        <v>84</v>
+      </c>
+      <c r="P16" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>86</v>
+      </c>
+      <c r="R16" t="s">
+        <v>147</v>
+      </c>
+      <c r="S16" t="s">
+        <v>148</v>
+      </c>
+      <c r="T16" t="s">
+        <v>99</v>
+      </c>
+      <c r="U16" t="s">
+        <v>149</v>
+      </c>
+      <c r="V16" t="s">
+        <v>89</v>
+      </c>
+      <c r="W16" t="s">
+        <v>109</v>
+      </c>
+      <c r="X16" t="s">
+        <v>150</v>
+      </c>
+      <c r="Y16" t="s">
+        <v>151</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>152</v>
+      </c>
+      <c r="AA16" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="19" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="20" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>154</v>
+      </c>
+      <c r="B20" t="s">
+        <v>155</v>
+      </c>
+      <c r="C20" t="s">
+        <v>156</v>
+      </c>
+      <c r="D20" t="s">
+        <v>157</v>
+      </c>
+      <c r="E20" t="s">
+        <v>158</v>
+      </c>
+      <c r="F20" t="s">
+        <v>159</v>
+      </c>
+      <c r="G20" t="s">
+        <v>160</v>
+      </c>
+      <c r="H20" t="s">
+        <v>161</v>
+      </c>
+      <c r="I20" t="s">
+        <v>162</v>
+      </c>
+      <c r="J20" t="s">
+        <v>163</v>
+      </c>
+      <c r="K20" t="s">
+        <v>164</v>
+      </c>
+      <c r="L20" t="s">
+        <v>165</v>
+      </c>
+      <c r="M20" t="s">
+        <v>166</v>
+      </c>
+      <c r="N20" t="s">
+        <v>167</v>
+      </c>
+      <c r="O20" t="s">
+        <v>168</v>
+      </c>
+      <c r="P20" t="s">
+        <v>169</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>170</v>
+      </c>
+      <c r="R20" t="s">
+        <v>171</v>
+      </c>
+      <c r="S20" t="s">
+        <v>172</v>
+      </c>
+      <c r="T20" t="s">
+        <v>173</v>
+      </c>
+      <c r="U20" t="s">
+        <v>174</v>
+      </c>
+      <c r="V20" t="s">
+        <v>175</v>
+      </c>
+      <c r="W20" t="s">
+        <v>176</v>
+      </c>
+      <c r="X20" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="21" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>15</v>
+      </c>
+      <c r="B21" t="s">
         <v>16</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C21" t="s">
         <v>17</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D21" t="s">
         <v>18</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E21" t="s">
         <v>19</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F21" t="s">
         <v>20</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G21" t="s">
         <v>21</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H21" t="s">
         <v>22</v>
       </c>
-      <c r="H4" t="s">
+      <c r="I21" t="s">
         <v>23</v>
       </c>
-      <c r="I4" t="s">
+      <c r="J21" t="s">
         <v>24</v>
       </c>
-      <c r="J4" t="s">
+      <c r="K21" t="s">
         <v>25</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L21" t="s">
         <v>26</v>
       </c>
-      <c r="L4" t="s">
-        <v>27</v>
-      </c>
-      <c r="M4" t="s">
-        <v>28</v>
-      </c>
-      <c r="N4" t="s">
-        <v>29</v>
-      </c>
-      <c r="O4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="8" spans="1:48" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="9" spans="1:48" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>32</v>
-      </c>
-      <c r="B9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C9" t="s">
-        <v>34</v>
-      </c>
-      <c r="D9" t="s">
-        <v>35</v>
-      </c>
-      <c r="E9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F9" t="s">
-        <v>37</v>
-      </c>
-      <c r="G9" t="s">
-        <v>38</v>
-      </c>
-      <c r="H9" t="s">
-        <v>39</v>
-      </c>
-      <c r="I9" t="s">
-        <v>40</v>
-      </c>
-      <c r="J9" t="s">
-        <v>41</v>
-      </c>
-      <c r="K9" t="s">
-        <v>42</v>
-      </c>
-      <c r="L9" t="s">
-        <v>43</v>
-      </c>
-      <c r="M9" t="s">
-        <v>44</v>
-      </c>
-      <c r="N9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O9" t="s">
-        <v>46</v>
-      </c>
-      <c r="P9" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>48</v>
-      </c>
-      <c r="R9" t="s">
-        <v>49</v>
-      </c>
-      <c r="S9" t="s">
-        <v>50</v>
-      </c>
-      <c r="T9" t="s">
-        <v>51</v>
-      </c>
-      <c r="U9" t="s">
-        <v>52</v>
-      </c>
-      <c r="V9" t="s">
-        <v>53</v>
-      </c>
-      <c r="W9" t="s">
-        <v>54</v>
-      </c>
-      <c r="X9" t="s">
-        <v>55</v>
-      </c>
-      <c r="Y9" t="s">
-        <v>56</v>
-      </c>
-      <c r="Z9" t="s">
-        <v>57</v>
-      </c>
-      <c r="AA9" t="s">
-        <v>58</v>
-      </c>
-      <c r="AB9" t="s">
-        <v>59</v>
-      </c>
-      <c r="AC9" t="s">
-        <v>60</v>
-      </c>
-      <c r="AD9" t="s">
-        <v>61</v>
-      </c>
-      <c r="AE9" t="s">
-        <v>62</v>
-      </c>
-      <c r="AF9" t="s">
-        <v>63</v>
-      </c>
-      <c r="AG9" t="s">
-        <v>64</v>
-      </c>
-      <c r="AH9" t="s">
-        <v>65</v>
-      </c>
-      <c r="AI9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AJ9" t="s">
-        <v>67</v>
-      </c>
-      <c r="AK9" t="s">
-        <v>68</v>
-      </c>
-      <c r="AL9" t="s">
-        <v>69</v>
-      </c>
-      <c r="AM9" t="s">
-        <v>70</v>
-      </c>
-      <c r="AN9" t="s">
-        <v>71</v>
-      </c>
-      <c r="AO9" t="s">
-        <v>72</v>
-      </c>
-      <c r="AP9" t="s">
-        <v>73</v>
-      </c>
-      <c r="AQ9" t="s">
-        <v>74</v>
-      </c>
-      <c r="AR9" t="s">
-        <v>75</v>
-      </c>
-      <c r="AS9" t="s">
-        <v>76</v>
-      </c>
-      <c r="AT9" t="s">
-        <v>77</v>
-      </c>
-      <c r="AU9" t="s">
-        <v>78</v>
-      </c>
-      <c r="AV9" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="10" spans="1:48" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>80</v>
-      </c>
-      <c r="B10" t="s">
-        <v>81</v>
-      </c>
-      <c r="C10" t="s">
-        <v>18</v>
-      </c>
-      <c r="D10" t="s">
-        <v>82</v>
-      </c>
-      <c r="E10" t="s">
-        <v>22</v>
-      </c>
-      <c r="F10" t="s">
-        <v>23</v>
-      </c>
-      <c r="G10" t="s">
-        <v>24</v>
-      </c>
-      <c r="H10" t="s">
-        <v>25</v>
-      </c>
-      <c r="I10" t="s">
-        <v>26</v>
-      </c>
-      <c r="J10" t="s">
-        <v>27</v>
-      </c>
-      <c r="K10" t="s">
-        <v>83</v>
-      </c>
-      <c r="L10" t="s">
-        <v>19</v>
-      </c>
-      <c r="M10" t="s">
-        <v>84</v>
-      </c>
-      <c r="N10" t="s">
-        <v>85</v>
-      </c>
-      <c r="O10" t="s">
-        <v>86</v>
-      </c>
-      <c r="P10" t="s">
-        <v>87</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>88</v>
-      </c>
-      <c r="R10" t="s">
-        <v>89</v>
-      </c>
-      <c r="S10" t="s">
-        <v>90</v>
-      </c>
-      <c r="T10" t="s">
-        <v>91</v>
-      </c>
-      <c r="U10" t="s">
-        <v>92</v>
-      </c>
-      <c r="V10" t="s">
-        <v>93</v>
-      </c>
-      <c r="W10" t="s">
-        <v>94</v>
-      </c>
-      <c r="X10" t="s">
-        <v>95</v>
-      </c>
-      <c r="Y10" t="s">
-        <v>96</v>
-      </c>
-      <c r="Z10" t="s">
-        <v>97</v>
-      </c>
-      <c r="AA10" t="s">
-        <v>98</v>
-      </c>
-      <c r="AB10" t="s">
-        <v>99</v>
-      </c>
-      <c r="AC10" t="s">
-        <v>100</v>
-      </c>
-      <c r="AD10" t="s">
-        <v>101</v>
-      </c>
-      <c r="AE10" t="s">
-        <v>102</v>
-      </c>
-      <c r="AF10" t="s">
-        <v>103</v>
-      </c>
-      <c r="AG10" t="s">
-        <v>104</v>
-      </c>
-      <c r="AH10" t="s">
-        <v>105</v>
-      </c>
-      <c r="AI10" t="s">
-        <v>106</v>
-      </c>
-      <c r="AJ10" t="s">
-        <v>107</v>
-      </c>
-      <c r="AK10" t="s">
-        <v>108</v>
-      </c>
-      <c r="AL10" t="s">
-        <v>109</v>
-      </c>
-      <c r="AM10" t="s">
-        <v>110</v>
-      </c>
-      <c r="AN10" t="s">
-        <v>111</v>
-      </c>
-      <c r="AO10" t="s">
-        <v>112</v>
-      </c>
-      <c r="AP10" t="s">
-        <v>113</v>
-      </c>
-      <c r="AQ10" t="s">
-        <v>114</v>
-      </c>
-      <c r="AR10" t="s">
-        <v>115</v>
-      </c>
-      <c r="AS10" t="s">
-        <v>116</v>
-      </c>
-      <c r="AT10" t="s">
-        <v>117</v>
-      </c>
-      <c r="AU10" t="s">
-        <v>118</v>
-      </c>
-      <c r="AV10" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="14" spans="1:48" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="15" spans="1:48" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>120</v>
-      </c>
-      <c r="B15" t="s">
-        <v>121</v>
-      </c>
-      <c r="C15" t="s">
-        <v>122</v>
-      </c>
-      <c r="D15" t="s">
-        <v>123</v>
-      </c>
-      <c r="E15" t="s">
-        <v>124</v>
-      </c>
-      <c r="F15" t="s">
-        <v>125</v>
-      </c>
-      <c r="G15" t="s">
-        <v>126</v>
-      </c>
-      <c r="H15" t="s">
-        <v>127</v>
-      </c>
-      <c r="I15" t="s">
-        <v>128</v>
-      </c>
-      <c r="J15" t="s">
-        <v>129</v>
-      </c>
-      <c r="K15" t="s">
-        <v>130</v>
-      </c>
-      <c r="L15" t="s">
-        <v>131</v>
-      </c>
-      <c r="M15" t="s">
-        <v>132</v>
-      </c>
-      <c r="N15" t="s">
-        <v>133</v>
-      </c>
-      <c r="O15" t="s">
-        <v>134</v>
-      </c>
-      <c r="P15" t="s">
-        <v>135</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>136</v>
-      </c>
-      <c r="R15" t="s">
-        <v>137</v>
-      </c>
-      <c r="S15" t="s">
-        <v>138</v>
-      </c>
-      <c r="T15" t="s">
-        <v>139</v>
-      </c>
-      <c r="U15" t="s">
-        <v>140</v>
-      </c>
-      <c r="V15" t="s">
-        <v>141</v>
-      </c>
-      <c r="W15" t="s">
-        <v>142</v>
-      </c>
-      <c r="X15" t="s">
-        <v>143</v>
-      </c>
-      <c r="Y15" t="s">
-        <v>144</v>
-      </c>
-      <c r="Z15" t="s">
-        <v>145</v>
-      </c>
-      <c r="AA15" t="s">
-        <v>146</v>
-      </c>
-      <c r="AB15" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="16" spans="1:48" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>80</v>
-      </c>
-      <c r="B16" t="s">
-        <v>81</v>
-      </c>
-      <c r="C16" t="s">
-        <v>81</v>
-      </c>
-      <c r="D16" t="s">
-        <v>18</v>
-      </c>
-      <c r="E16" t="s">
-        <v>82</v>
-      </c>
-      <c r="F16" t="s">
-        <v>22</v>
-      </c>
-      <c r="G16" t="s">
-        <v>23</v>
-      </c>
-      <c r="H16" t="s">
-        <v>24</v>
-      </c>
-      <c r="I16" t="s">
-        <v>25</v>
-      </c>
-      <c r="J16" t="s">
-        <v>26</v>
-      </c>
-      <c r="K16" t="s">
-        <v>27</v>
-      </c>
-      <c r="L16" t="s">
-        <v>83</v>
-      </c>
-      <c r="M16" t="s">
-        <v>19</v>
-      </c>
-      <c r="N16" t="s">
-        <v>84</v>
-      </c>
-      <c r="O16" t="s">
-        <v>85</v>
-      </c>
-      <c r="P16" t="s">
-        <v>86</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>87</v>
-      </c>
-      <c r="R16" t="s">
-        <v>148</v>
-      </c>
-      <c r="S16" t="s">
-        <v>149</v>
-      </c>
-      <c r="T16" t="s">
-        <v>100</v>
-      </c>
-      <c r="U16" t="s">
-        <v>150</v>
-      </c>
-      <c r="V16" t="s">
-        <v>90</v>
-      </c>
-      <c r="W16" t="s">
-        <v>110</v>
-      </c>
-      <c r="X16" t="s">
-        <v>151</v>
-      </c>
-      <c r="Y16" t="s">
-        <v>152</v>
-      </c>
-      <c r="Z16" t="s">
-        <v>153</v>
-      </c>
-      <c r="AA16" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>155</v>
-      </c>
-      <c r="B20" t="s">
-        <v>156</v>
-      </c>
-      <c r="C20" t="s">
-        <v>157</v>
-      </c>
-      <c r="D20" t="s">
-        <v>158</v>
-      </c>
-      <c r="E20" t="s">
-        <v>159</v>
-      </c>
-      <c r="F20" t="s">
-        <v>160</v>
-      </c>
-      <c r="G20" t="s">
-        <v>161</v>
-      </c>
-      <c r="H20" t="s">
-        <v>162</v>
-      </c>
-      <c r="I20" t="s">
-        <v>163</v>
-      </c>
-      <c r="J20" t="s">
-        <v>164</v>
-      </c>
-      <c r="K20" t="s">
-        <v>165</v>
-      </c>
-      <c r="L20" t="s">
-        <v>166</v>
-      </c>
-      <c r="M20" t="s">
-        <v>167</v>
-      </c>
-      <c r="N20" t="s">
-        <v>168</v>
-      </c>
-      <c r="O20" t="s">
-        <v>169</v>
-      </c>
-      <c r="P20" t="s">
-        <v>170</v>
-      </c>
-      <c r="Q20" t="s">
-        <v>171</v>
-      </c>
-      <c r="R20" t="s">
-        <v>172</v>
-      </c>
-      <c r="S20" t="s">
-        <v>173</v>
-      </c>
-      <c r="T20" t="s">
-        <v>174</v>
-      </c>
-      <c r="U20" t="s">
-        <v>175</v>
-      </c>
-      <c r="V20" t="s">
-        <v>176</v>
-      </c>
-      <c r="W20" t="s">
-        <v>177</v>
-      </c>
-      <c r="X20" t="s">
+      <c r="M21" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>16</v>
-      </c>
-      <c r="B21" t="s">
-        <v>17</v>
-      </c>
-      <c r="C21" t="s">
-        <v>18</v>
-      </c>
-      <c r="D21" t="s">
-        <v>19</v>
-      </c>
-      <c r="E21" t="s">
-        <v>20</v>
-      </c>
-      <c r="F21" t="s">
-        <v>21</v>
-      </c>
-      <c r="G21" t="s">
-        <v>22</v>
-      </c>
-      <c r="H21" t="s">
-        <v>23</v>
-      </c>
-      <c r="I21" t="s">
-        <v>24</v>
-      </c>
-      <c r="J21" t="s">
-        <v>25</v>
-      </c>
-      <c r="K21" t="s">
-        <v>26</v>
-      </c>
-      <c r="L21" t="s">
-        <v>27</v>
-      </c>
-      <c r="M21" t="s">
+      <c r="N21" t="s">
         <v>179</v>
       </c>
-      <c r="N21" t="s">
+      <c r="O21" t="s">
         <v>180</v>
       </c>
-      <c r="O21" t="s">
+      <c r="P21" t="s">
         <v>181</v>
       </c>
-      <c r="P21" t="s">
+      <c r="Q21" t="s">
         <v>182</v>
       </c>
-      <c r="Q21" t="s">
+      <c r="R21" t="s">
+        <v>182</v>
+      </c>
+      <c r="S21" t="s">
         <v>183</v>
       </c>
-      <c r="R21" t="s">
-        <v>183</v>
-      </c>
-      <c r="S21" t="s">
+      <c r="T21" t="s">
         <v>184</v>
       </c>
-      <c r="T21" t="s">
+      <c r="U21" t="s">
         <v>185</v>
       </c>
-      <c r="U21" t="s">
+      <c r="V21" t="s">
         <v>186</v>
       </c>
-      <c r="V21" t="s">
+      <c r="W21" t="s">
         <v>187</v>
       </c>
-      <c r="W21" t="s">
+      <c r="X21" t="s">
         <v>188</v>
-      </c>
-      <c r="X21" t="s">
-        <v>189</v>
       </c>
     </row>
   </sheetData>
